--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3970" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9C0C187-E26F-47C7-8BB9-4210AB72D3AF}"/>
+  <xr:revisionPtr revIDLastSave="4091" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D4E3901-F6CD-4B60-93C4-75C7D966498A}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="144">
   <si>
     <t>Boneco</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,6 +490,14 @@
       <color rgb="FF000000"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -512,11 +520,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O342"/>
+  <dimension ref="A1:O369"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -12796,6 +12805,814 @@
         <v>0</v>
       </c>
     </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>1</v>
+      </c>
+      <c r="C343">
+        <v>5</v>
+      </c>
+      <c r="D343">
+        <v>3</v>
+      </c>
+      <c r="E343">
+        <v>1</v>
+      </c>
+      <c r="F343">
+        <v>2</v>
+      </c>
+      <c r="G343">
+        <v>1</v>
+      </c>
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
+        <v>0</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343">
+        <v>0</v>
+      </c>
+      <c r="L343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>134</v>
+      </c>
+      <c r="C344">
+        <v>5</v>
+      </c>
+      <c r="D344">
+        <v>3</v>
+      </c>
+      <c r="E344">
+        <v>1</v>
+      </c>
+      <c r="F344">
+        <v>3</v>
+      </c>
+      <c r="G344">
+        <v>1</v>
+      </c>
+      <c r="H344">
+        <v>1</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>23</v>
+      </c>
+      <c r="C345">
+        <v>5</v>
+      </c>
+      <c r="D345">
+        <v>3</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+      <c r="F345">
+        <v>2</v>
+      </c>
+      <c r="G345">
+        <v>1</v>
+      </c>
+      <c r="H345">
+        <v>1</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>0</v>
+      </c>
+      <c r="K345">
+        <v>0</v>
+      </c>
+      <c r="L345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>128</v>
+      </c>
+      <c r="C346">
+        <v>5</v>
+      </c>
+      <c r="D346">
+        <v>3</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+      <c r="F346">
+        <v>2</v>
+      </c>
+      <c r="G346">
+        <v>1</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
+        <v>0</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>0</v>
+      </c>
+      <c r="L346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>20</v>
+      </c>
+      <c r="C347">
+        <v>5</v>
+      </c>
+      <c r="D347">
+        <v>3</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+      <c r="F347">
+        <v>1</v>
+      </c>
+      <c r="G347">
+        <v>1</v>
+      </c>
+      <c r="H347">
+        <v>1</v>
+      </c>
+      <c r="I347">
+        <v>0</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347">
+        <v>0</v>
+      </c>
+      <c r="L347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>28</v>
+      </c>
+      <c r="C348">
+        <v>2</v>
+      </c>
+      <c r="D348">
+        <v>2</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+      <c r="F348">
+        <v>0</v>
+      </c>
+      <c r="G348">
+        <v>1</v>
+      </c>
+      <c r="H348">
+        <v>0</v>
+      </c>
+      <c r="I348">
+        <v>0</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>0</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>140</v>
+      </c>
+      <c r="C349">
+        <v>2</v>
+      </c>
+      <c r="D349">
+        <v>2</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+      <c r="F349">
+        <v>0</v>
+      </c>
+      <c r="G349">
+        <v>1</v>
+      </c>
+      <c r="H349">
+        <v>0</v>
+      </c>
+      <c r="I349">
+        <v>0</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>4</v>
+      </c>
+      <c r="C350">
+        <v>2</v>
+      </c>
+      <c r="D350">
+        <v>2</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+      <c r="F350">
+        <v>2</v>
+      </c>
+      <c r="G350">
+        <v>1</v>
+      </c>
+      <c r="H350">
+        <v>0</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350">
+        <v>0</v>
+      </c>
+      <c r="L350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>50</v>
+      </c>
+      <c r="C351">
+        <v>2</v>
+      </c>
+      <c r="D351">
+        <v>2</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+      <c r="F351">
+        <v>0</v>
+      </c>
+      <c r="G351">
+        <v>1</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+      <c r="I351">
+        <v>0</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351">
+        <v>0</v>
+      </c>
+      <c r="L351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>41</v>
+      </c>
+      <c r="C352">
+        <v>2</v>
+      </c>
+      <c r="D352">
+        <v>2</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+      <c r="F352">
+        <v>1</v>
+      </c>
+      <c r="G352">
+        <v>1</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352">
+        <v>0</v>
+      </c>
+      <c r="L352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>3</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353">
+        <v>1</v>
+      </c>
+      <c r="E353">
+        <v>3</v>
+      </c>
+      <c r="F353">
+        <v>0</v>
+      </c>
+      <c r="G353">
+        <v>1</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+      <c r="I353">
+        <v>1</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>0</v>
+      </c>
+      <c r="L353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>36</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+      <c r="D354">
+        <v>1</v>
+      </c>
+      <c r="E354">
+        <v>3</v>
+      </c>
+      <c r="F354">
+        <v>0</v>
+      </c>
+      <c r="G354">
+        <v>1</v>
+      </c>
+      <c r="H354">
+        <v>0</v>
+      </c>
+      <c r="I354">
+        <v>1</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>26</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355">
+        <v>1</v>
+      </c>
+      <c r="E355">
+        <v>3</v>
+      </c>
+      <c r="F355">
+        <v>0</v>
+      </c>
+      <c r="G355">
+        <v>1</v>
+      </c>
+      <c r="H355">
+        <v>0</v>
+      </c>
+      <c r="I355">
+        <v>1</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>0</v>
+      </c>
+      <c r="L355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>6</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+      <c r="D356">
+        <v>1</v>
+      </c>
+      <c r="E356">
+        <v>3</v>
+      </c>
+      <c r="F356">
+        <v>0</v>
+      </c>
+      <c r="G356">
+        <v>1</v>
+      </c>
+      <c r="H356">
+        <v>0</v>
+      </c>
+      <c r="I356">
+        <v>1</v>
+      </c>
+      <c r="J356">
+        <v>0</v>
+      </c>
+      <c r="K356">
+        <v>0</v>
+      </c>
+      <c r="L356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>32</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+      <c r="D357">
+        <v>1</v>
+      </c>
+      <c r="E357">
+        <v>3</v>
+      </c>
+      <c r="F357">
+        <v>1</v>
+      </c>
+      <c r="G357">
+        <v>1</v>
+      </c>
+      <c r="H357">
+        <v>0</v>
+      </c>
+      <c r="I357">
+        <v>1</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357">
+        <v>0</v>
+      </c>
+      <c r="L357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>109</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+      <c r="D358">
+        <v>2</v>
+      </c>
+      <c r="E358">
+        <v>3</v>
+      </c>
+      <c r="F358">
+        <v>0</v>
+      </c>
+      <c r="G358">
+        <v>1</v>
+      </c>
+      <c r="H358">
+        <v>0</v>
+      </c>
+      <c r="I358">
+        <v>0</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358">
+        <v>0</v>
+      </c>
+      <c r="L358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>30</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+      <c r="D359">
+        <v>2</v>
+      </c>
+      <c r="E359">
+        <v>3</v>
+      </c>
+      <c r="F359">
+        <v>0</v>
+      </c>
+      <c r="G359">
+        <v>1</v>
+      </c>
+      <c r="H359">
+        <v>0</v>
+      </c>
+      <c r="I359">
+        <v>0</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+      <c r="K359">
+        <v>0</v>
+      </c>
+      <c r="L359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>115</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+      <c r="D360">
+        <v>2</v>
+      </c>
+      <c r="E360">
+        <v>3</v>
+      </c>
+      <c r="F360">
+        <v>0</v>
+      </c>
+      <c r="G360">
+        <v>1</v>
+      </c>
+      <c r="H360">
+        <v>0</v>
+      </c>
+      <c r="I360">
+        <v>0</v>
+      </c>
+      <c r="J360">
+        <v>0</v>
+      </c>
+      <c r="K360">
+        <v>0</v>
+      </c>
+      <c r="L360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>130</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+      <c r="D361">
+        <v>2</v>
+      </c>
+      <c r="E361">
+        <v>3</v>
+      </c>
+      <c r="F361">
+        <v>1</v>
+      </c>
+      <c r="G361">
+        <v>1</v>
+      </c>
+      <c r="H361">
+        <v>0</v>
+      </c>
+      <c r="I361">
+        <v>0</v>
+      </c>
+      <c r="J361">
+        <v>0</v>
+      </c>
+      <c r="K361">
+        <v>0</v>
+      </c>
+      <c r="L361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>5</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+      <c r="D362">
+        <v>2</v>
+      </c>
+      <c r="E362">
+        <v>3</v>
+      </c>
+      <c r="F362">
+        <v>0</v>
+      </c>
+      <c r="G362">
+        <v>1</v>
+      </c>
+      <c r="H362">
+        <v>0</v>
+      </c>
+      <c r="I362">
+        <v>0</v>
+      </c>
+      <c r="J362">
+        <v>0</v>
+      </c>
+      <c r="K362">
+        <v>0</v>
+      </c>
+      <c r="L362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>107</v>
+      </c>
+      <c r="C363">
+        <v>4</v>
+      </c>
+      <c r="D363">
+        <v>3</v>
+      </c>
+      <c r="E363">
+        <v>3</v>
+      </c>
+      <c r="F363">
+        <v>0</v>
+      </c>
+      <c r="G363">
+        <v>1</v>
+      </c>
+      <c r="H363">
+        <v>1</v>
+      </c>
+      <c r="I363">
+        <v>0</v>
+      </c>
+      <c r="J363">
+        <v>0</v>
+      </c>
+      <c r="K363">
+        <v>6</v>
+      </c>
+      <c r="L363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>17</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>1</v>
+      </c>
+      <c r="E364">
+        <v>1</v>
+      </c>
+      <c r="F364">
+        <v>0</v>
+      </c>
+      <c r="G364">
+        <v>1</v>
+      </c>
+      <c r="H364">
+        <v>0</v>
+      </c>
+      <c r="I364">
+        <v>0</v>
+      </c>
+      <c r="J364">
+        <v>0</v>
+      </c>
+      <c r="K364">
+        <v>3</v>
+      </c>
+      <c r="L364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>141</v>
+      </c>
+      <c r="C365">
+        <v>4</v>
+      </c>
+      <c r="D365">
+        <v>2</v>
+      </c>
+      <c r="E365">
+        <v>4</v>
+      </c>
+      <c r="F365">
+        <v>0</v>
+      </c>
+      <c r="G365">
+        <v>1</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+      <c r="I365">
+        <v>0</v>
+      </c>
+      <c r="J365">
+        <v>0</v>
+      </c>
+      <c r="K365">
+        <v>5</v>
+      </c>
+      <c r="L365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A369" s="2"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4091" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D4E3901-F6CD-4B60-93C4-75C7D966498A}"/>
+  <xr:revisionPtr revIDLastSave="4206" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5A1D147-A0FD-4A34-B82E-327D03097F09}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="146">
   <si>
     <t>Boneco</t>
   </si>
@@ -471,13 +471,19 @@
   </si>
   <si>
     <t xml:space="preserve">João </t>
+  </si>
+  <si>
+    <t>Bernardo</t>
+  </si>
+  <si>
+    <t>Alessandro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,14 +496,6 @@
       <color rgb="FF000000"/>
       <name val="Courier New"/>
       <family val="3"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -525,7 +523,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O369"/>
+  <dimension ref="A1:O387"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -13610,8 +13608,775 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A369" s="2"/>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>57</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>1</v>
+      </c>
+      <c r="E366">
+        <v>4</v>
+      </c>
+      <c r="F366">
+        <v>0</v>
+      </c>
+      <c r="G366">
+        <v>1</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+      <c r="I366">
+        <v>1</v>
+      </c>
+      <c r="J366">
+        <v>0</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>128</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>1</v>
+      </c>
+      <c r="E367">
+        <v>4</v>
+      </c>
+      <c r="F367">
+        <v>0</v>
+      </c>
+      <c r="G367">
+        <v>1</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+      <c r="I367">
+        <v>1</v>
+      </c>
+      <c r="J367">
+        <v>0</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>20</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>1</v>
+      </c>
+      <c r="E368">
+        <v>4</v>
+      </c>
+      <c r="F368">
+        <v>0</v>
+      </c>
+      <c r="G368">
+        <v>1</v>
+      </c>
+      <c r="H368">
+        <v>0</v>
+      </c>
+      <c r="I368">
+        <v>1</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368">
+        <v>0</v>
+      </c>
+      <c r="L368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A369" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>1</v>
+      </c>
+      <c r="E369">
+        <v>4</v>
+      </c>
+      <c r="F369">
+        <v>0</v>
+      </c>
+      <c r="G369">
+        <v>1</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+      <c r="I369">
+        <v>1</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369">
+        <v>0</v>
+      </c>
+      <c r="L369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A370" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>1</v>
+      </c>
+      <c r="E370">
+        <v>4</v>
+      </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
+      <c r="G370">
+        <v>1</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+      <c r="I370">
+        <v>1</v>
+      </c>
+      <c r="J370">
+        <v>0</v>
+      </c>
+      <c r="K370">
+        <v>0</v>
+      </c>
+      <c r="L370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A371" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C371">
+        <v>3</v>
+      </c>
+      <c r="D371">
+        <v>1</v>
+      </c>
+      <c r="E371">
+        <v>3</v>
+      </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
+      <c r="G371">
+        <v>1</v>
+      </c>
+      <c r="H371">
+        <v>0</v>
+      </c>
+      <c r="I371">
+        <v>0</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371">
+        <v>0</v>
+      </c>
+      <c r="L371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A372" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C372">
+        <v>3</v>
+      </c>
+      <c r="D372">
+        <v>1</v>
+      </c>
+      <c r="E372">
+        <v>3</v>
+      </c>
+      <c r="F372">
+        <v>0</v>
+      </c>
+      <c r="G372">
+        <v>1</v>
+      </c>
+      <c r="H372">
+        <v>0</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372">
+        <v>0</v>
+      </c>
+      <c r="L372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A373" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C373">
+        <v>3</v>
+      </c>
+      <c r="D373">
+        <v>1</v>
+      </c>
+      <c r="E373">
+        <v>3</v>
+      </c>
+      <c r="F373">
+        <v>0</v>
+      </c>
+      <c r="G373">
+        <v>1</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A374" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C374">
+        <v>3</v>
+      </c>
+      <c r="D374">
+        <v>1</v>
+      </c>
+      <c r="E374">
+        <v>3</v>
+      </c>
+      <c r="F374">
+        <v>0</v>
+      </c>
+      <c r="G374">
+        <v>1</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+      <c r="I374">
+        <v>0</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374">
+        <v>0</v>
+      </c>
+      <c r="L374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A375" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C375">
+        <v>3</v>
+      </c>
+      <c r="D375">
+        <v>1</v>
+      </c>
+      <c r="E375">
+        <v>3</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>1</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+      <c r="I375">
+        <v>0</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375">
+        <v>0</v>
+      </c>
+      <c r="L375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A376" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C376">
+        <v>2</v>
+      </c>
+      <c r="D376">
+        <v>2</v>
+      </c>
+      <c r="E376">
+        <v>2</v>
+      </c>
+      <c r="F376">
+        <v>1</v>
+      </c>
+      <c r="G376">
+        <v>1</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+      <c r="I376">
+        <v>0</v>
+      </c>
+      <c r="J376">
+        <v>0</v>
+      </c>
+      <c r="K376">
+        <v>0</v>
+      </c>
+      <c r="L376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A377" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C377">
+        <v>2</v>
+      </c>
+      <c r="D377">
+        <v>2</v>
+      </c>
+      <c r="E377">
+        <v>2</v>
+      </c>
+      <c r="F377">
+        <v>0</v>
+      </c>
+      <c r="G377">
+        <v>1</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A378" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C378">
+        <v>2</v>
+      </c>
+      <c r="D378">
+        <v>2</v>
+      </c>
+      <c r="E378">
+        <v>2</v>
+      </c>
+      <c r="F378">
+        <v>1</v>
+      </c>
+      <c r="G378">
+        <v>1</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+      <c r="I378">
+        <v>0</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>0</v>
+      </c>
+      <c r="L378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A379" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C379">
+        <v>2</v>
+      </c>
+      <c r="D379">
+        <v>2</v>
+      </c>
+      <c r="E379">
+        <v>2</v>
+      </c>
+      <c r="F379">
+        <v>1</v>
+      </c>
+      <c r="G379">
+        <v>1</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+      <c r="I379">
+        <v>0</v>
+      </c>
+      <c r="J379">
+        <v>0</v>
+      </c>
+      <c r="K379">
+        <v>0</v>
+      </c>
+      <c r="L379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A380" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C380">
+        <v>2</v>
+      </c>
+      <c r="D380">
+        <v>2</v>
+      </c>
+      <c r="E380">
+        <v>2</v>
+      </c>
+      <c r="F380">
+        <v>0</v>
+      </c>
+      <c r="G380">
+        <v>1</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+      <c r="J380">
+        <v>0</v>
+      </c>
+      <c r="K380">
+        <v>0</v>
+      </c>
+      <c r="L380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A381" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C381">
+        <v>5</v>
+      </c>
+      <c r="D381">
+        <v>2</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+      <c r="F381">
+        <v>1</v>
+      </c>
+      <c r="G381">
+        <v>1</v>
+      </c>
+      <c r="H381">
+        <v>1</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+      <c r="J381">
+        <v>0</v>
+      </c>
+      <c r="K381">
+        <v>0</v>
+      </c>
+      <c r="L381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A382" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C382">
+        <v>5</v>
+      </c>
+      <c r="D382">
+        <v>2</v>
+      </c>
+      <c r="E382">
+        <v>1</v>
+      </c>
+      <c r="F382">
+        <v>3</v>
+      </c>
+      <c r="G382">
+        <v>1</v>
+      </c>
+      <c r="H382">
+        <v>1</v>
+      </c>
+      <c r="I382">
+        <v>0</v>
+      </c>
+      <c r="J382">
+        <v>0</v>
+      </c>
+      <c r="K382">
+        <v>0</v>
+      </c>
+      <c r="L382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A383" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C383">
+        <v>5</v>
+      </c>
+      <c r="D383">
+        <v>2</v>
+      </c>
+      <c r="E383">
+        <v>1</v>
+      </c>
+      <c r="F383">
+        <v>5</v>
+      </c>
+      <c r="G383">
+        <v>1</v>
+      </c>
+      <c r="H383">
+        <v>1</v>
+      </c>
+      <c r="I383">
+        <v>0</v>
+      </c>
+      <c r="J383">
+        <v>0</v>
+      </c>
+      <c r="K383">
+        <v>0</v>
+      </c>
+      <c r="L383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>36</v>
+      </c>
+      <c r="C384">
+        <v>5</v>
+      </c>
+      <c r="D384">
+        <v>2</v>
+      </c>
+      <c r="E384">
+        <v>1</v>
+      </c>
+      <c r="F384">
+        <v>0</v>
+      </c>
+      <c r="G384">
+        <v>1</v>
+      </c>
+      <c r="H384">
+        <v>1</v>
+      </c>
+      <c r="I384">
+        <v>0</v>
+      </c>
+      <c r="J384">
+        <v>0</v>
+      </c>
+      <c r="K384">
+        <v>0</v>
+      </c>
+      <c r="L384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>145</v>
+      </c>
+      <c r="C385">
+        <v>5</v>
+      </c>
+      <c r="D385">
+        <v>2</v>
+      </c>
+      <c r="E385">
+        <v>1</v>
+      </c>
+      <c r="F385">
+        <v>0</v>
+      </c>
+      <c r="G385">
+        <v>1</v>
+      </c>
+      <c r="H385">
+        <v>1</v>
+      </c>
+      <c r="I385">
+        <v>0</v>
+      </c>
+      <c r="J385">
+        <v>0</v>
+      </c>
+      <c r="K385">
+        <v>0</v>
+      </c>
+      <c r="L385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>17</v>
+      </c>
+      <c r="C386">
+        <v>4</v>
+      </c>
+      <c r="D386">
+        <v>3</v>
+      </c>
+      <c r="E386">
+        <v>5</v>
+      </c>
+      <c r="F386">
+        <v>0</v>
+      </c>
+      <c r="G386">
+        <v>1</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+      <c r="I386">
+        <v>0</v>
+      </c>
+      <c r="J386">
+        <v>0</v>
+      </c>
+      <c r="K386">
+        <v>9</v>
+      </c>
+      <c r="L386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>114</v>
+      </c>
+      <c r="C387">
+        <v>5</v>
+      </c>
+      <c r="D387">
+        <v>3</v>
+      </c>
+      <c r="E387">
+        <v>4</v>
+      </c>
+      <c r="F387">
+        <v>0</v>
+      </c>
+      <c r="G387">
+        <v>1</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+      <c r="I387">
+        <v>0</v>
+      </c>
+      <c r="J387">
+        <v>0</v>
+      </c>
+      <c r="K387">
+        <v>5</v>
+      </c>
+      <c r="L387">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
